--- a/parcelle.xlsx
+++ b/parcelle.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Formation\Desktop\P4\Robot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Formation\Desktop\P4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E0B0FF-7947-41DE-B376-C17E4EB2A088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF77A78-2B21-4398-8489-D64E37960438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{B1E90C9F-BD24-49E9-8A9B-9A736B504C21}"/>
+    <workbookView xWindow="5568" yWindow="3408" windowWidth="17280" windowHeight="8964" xr2:uid="{B1E90C9F-BD24-49E9-8A9B-9A736B504C21}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>Petit jardin des champs</t>
   </si>
@@ -113,9 +113,6 @@
     <t>2A205</t>
   </si>
   <si>
-    <t>2a205</t>
-  </si>
-  <si>
     <t>Terres de Lumroy</t>
   </si>
   <si>
@@ -159,6 +156,21 @@
   </si>
   <si>
     <t>Terrain 2 campagne</t>
+  </si>
+  <si>
+    <t>00000</t>
+  </si>
+  <si>
+    <t>2AA75</t>
+  </si>
+  <si>
+    <t>3A824</t>
+  </si>
+  <si>
+    <t>Viennes</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -194,8 +206,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D6CE6F-C543-4BAF-80A3-621E91BC4531}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
@@ -562,7 +575,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -602,16 +615,16 @@
     </row>
     <row r="4" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
       </c>
       <c r="C4">
         <v>45400</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>4.3</v>
@@ -622,16 +635,16 @@
     </row>
     <row r="5" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
       </c>
       <c r="C5">
         <v>33400</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>7</v>
@@ -661,6 +674,9 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -679,7 +695,10 @@
     </row>
     <row r="8" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C8">
         <v>72846</v>
@@ -701,6 +720,9 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
@@ -721,6 +743,9 @@
       <c r="C10">
         <v>91200</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="E10">
         <v>1</v>
       </c>
@@ -741,6 +766,9 @@
       <c r="D11" t="s">
         <v>15</v>
       </c>
+      <c r="E11" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="F11">
         <v>20</v>
       </c>
@@ -761,6 +789,9 @@
       <c r="E12">
         <v>20</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -824,19 +855,19 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
+        <v>33</v>
+      </c>
+      <c r="C16">
+        <v>33400</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -844,82 +875,182 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17">
-        <v>33400</v>
+        <v>77200</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17">
-        <v>-2</v>
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
       </c>
       <c r="C18">
         <v>77200</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="E18">
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>30</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
         <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
       </c>
       <c r="C19">
         <v>77200</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19">
         <v>40</v>
       </c>
-      <c r="F19">
-        <v>-3</v>
+      <c r="F19" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
         <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
       </c>
       <c r="C20">
         <v>77200</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20">
+        <v>-10</v>
+      </c>
+      <c r="F20">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F20" t="s">
-        <v>39</v>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>91200</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24">
+        <v>19</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25">
+        <v>91200</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
